--- a/tests/fixtures/Example_2026_Invoice_07162026.xlsx
+++ b/tests/fixtures/Example_2026_Invoice_07162026.xlsx
@@ -619,11 +619,11 @@
   <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.29" customWidth="1" min="1" max="1"/>
-    <col width="8.43" customWidth="1" min="2" max="2"/>
-    <col width="31.43" customWidth="1" min="3" max="3"/>
-    <col width="19.29" customWidth="1" min="4" max="4"/>
-    <col width="19.29" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9.140000000000001" customWidth="1" min="2" max="2"/>
+    <col width="32.14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">

--- a/tests/fixtures/Example_2026_Invoice_07162026.xlsx
+++ b/tests/fixtures/Example_2026_Invoice_07162026.xlsx
@@ -629,21 +629,21 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ACCESS MULTI-SPECIALTY MEDICAL CLINIC, INC.</t>
+          <t>YOUR CLINIC NAME, INC.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MICHAEL U. LEVINSON, MD, PH D.</t>
+          <t>JANE A. DOE, MD</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>BOARD CERTIFIED PSYCHIATRIST</t>
+          <t>BOARD CERTIFIED PHYSICIAN</t>
         </is>
       </c>
     </row>
@@ -651,28 +651,28 @@
     <row r="5" ht="15.95" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS: 25 EDWARDS COURT, SUITE 101, BURLINGAME, CA 94010</t>
+          <t>OFFICE ADDRESS: 123 MAIN STREET, SUITE 100, YOUR CITY, ST 00000</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.95" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MAILING ADDRESS: PO BOX 351, BURLINGAME, CA 94011</t>
+          <t>MAILING ADDRESS: PO BOX 000, YOUR CITY, ST 00000</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15.95" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EMAIL: ACCESS.MSMC@GMAIL.COM</t>
+          <t>EMAIL: BILLING@YOURCLINIC.COM</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15.95" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WEBSITE: https://accessmultispecialty.com/</t>
+          <t>WEBSITE: https://yourclinic.example.com/</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Please note we do not accept credit cards.
-1. Zelle access.msmc@gmail.com 
+1. Zelle billing@yourclinic.com 
    (IRA Billing and Mgmt)
-2. Check payable to: Michael Levinson, MD
-    PO Box 351, Burlingame, CA 94011</t>
+2. Check payable to: Jane A. Doe, MD
+    PO BOX 000, YOUR CITY, ST 00000</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>Provider Signature - Michael Levinson, MD</t>
+          <t>Provider Signature - Jane A. Doe, MD</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
   <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;8 If you have questions regarding your bill, please contact us at (415)857-1151._x000a_For current pricing, please visit: https://accessmultispecialty.com/pricing.html</oddFooter>
+    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;8 If you have questions regarding your bill, please contact us at (000)000-0000._x000a_For current pricing, please visit: https://yourclinic.example.com/pricing.html</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/tests/fixtures/Example_2026_Invoice_07162026.xlsx
+++ b/tests/fixtures/Example_2026_Invoice_07162026.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Invoice'!$21:$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Invoice'!$26:$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A$1:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00;\-\$#,##0.00;&quot;$ -&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,7 +74,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -86,48 +92,6 @@
       <top style="thin">
         <color rgb="00000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="double">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
       <bottom/>
     </border>
     <border>
@@ -182,11 +146,58 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="dashed">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="double">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,58 +208,62 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -616,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -700,307 +715,320 @@
     <row r="13" ht="15" customHeight="1"/>
     <row r="14" ht="15" customHeight="1"/>
     <row r="15" ht="12" customHeight="1"/>
-    <row r="16" ht="20.1" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>STATEMENT DATE:</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Payment due date:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="12" customHeight="1"/>
+    <row r="19" ht="17.1" customHeight="1">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>YOUR PORTION DUE:</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>AMOUNT ENCLOSED:</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="17.1" customHeight="1">
+      <c r="C20" s="8" t="n">
+        <v>721</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>- - - - -  Detach and retain for your records  - - - - -</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="12" customHeight="1"/>
+    <row r="23" ht="20.1" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>PATIENT STATEMENT</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1">
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>STATEMENT DATE:</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Payment due date:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>07/16/2026</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>08/17/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="12" customHeight="1"/>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="12" customHeight="1"/>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Service Date(s)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Amount Paid</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Copay/Deductible</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n">
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E27" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>01/29/2026</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="11" t="n">
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E28" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>02/12/2026</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="n">
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n">
         <v>500</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E29" s="19" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="11" t="n">
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E30" s="19" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>03/31/2026</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Med Management</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="11" t="n">
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E31" s="19" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="11" t="n">
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E32" s="19" t="n">
         <v>122</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>04/14/2026</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Med Management</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="11" t="n">
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E33" s="19" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>04/30/2026</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="11" t="n">
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E34" s="19" t="n">
         <v>122</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="12" t="inlineStr"/>
-      <c r="B30" s="12" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="20" t="inlineStr"/>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="14" t="n">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E35" s="22" t="n">
         <v>1221</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="15" t="inlineStr"/>
-      <c r="B31" s="15" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="23" t="inlineStr"/>
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="18" t="n">
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="26" t="n">
         <v>721</v>
       </c>
     </row>
-    <row r="32" ht="12" customHeight="1"/>
-    <row r="33" ht="17.1" customHeight="1">
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>YOUR PORTION DUE:</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>AMOUNT ENCLOSED:</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="17.1" customHeight="1">
-      <c r="C34" s="22" t="n">
-        <v>721</v>
-      </c>
-      <c r="D34" s="23" t="inlineStr"/>
-      <c r="E34" s="24" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
+    <row r="37" ht="12" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>_________________________________</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Provider Signature - Jane A. Doe, MD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="B25:C25"/>
+  <mergeCells count="28">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A10:B14"/>
     <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D34:E34"/>
     <mergeCell ref="D10:E14"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.65" top="0.4" bottom="0.6" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait"/>
